--- a/media/exports/reports/2026-10/people-helped.xlsx
+++ b/media/exports/reports/2026-10/people-helped.xlsx
@@ -831,7 +831,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>How many people did we help this month, and how many couldn't we reach?</t>
+          <t>How many people did you help this month, and how many couldn't you reach?</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: October 2026 to date · Data status: Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1185,7 +1185,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: October 2026 to date · Data status: Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>People we couldn't reach</t>
+          <t>People not reached</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
@@ -1310,7 +1310,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>People we couldn't reach</t>
+          <t>People not reached</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
@@ -1387,7 +1387,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>People we couldn't reach</t>
+          <t>People not reached</t>
         </is>
       </c>
       <c r="B27" s="16" t="n">
@@ -1703,7 +1703,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1794,7 +1794,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
+          <t>Period: October 2026 to date · Data status: Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
